--- a/测试文件/2320-detail/增值税销项.xlsx
+++ b/测试文件/2320-detail/增值税销项.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\epc-test\测试文件\2320-detail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{261225C5-E977-4AF1-94C8-B09F5CD27711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9606FB91-0C82-40C0-BEC6-8471FB027B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6795" yWindow="1770" windowWidth="21600" windowHeight="12825" xr2:uid="{41ADFF05-266D-4900-AA97-9CFAFEF5393A}"/>
+    <workbookView xWindow="7605" yWindow="2625" windowWidth="21600" windowHeight="11250" xr2:uid="{41ADFF05-266D-4900-AA97-9CFAFEF5393A}"/>
   </bookViews>
   <sheets>
     <sheet name="Ref 2_202512增值税销项 （样式）" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="\A">#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ref 2_202512增值税销项 （样式）'!#REF!</definedName>
@@ -62,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2590" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2588" uniqueCount="617">
   <si>
     <t>序号</t>
   </si>
@@ -1870,12 +1867,6 @@
   </si>
   <si>
     <t>0.06</t>
-  </si>
-  <si>
-    <t>20383591.90</t>
-  </si>
-  <si>
-    <t>1223015.54</t>
   </si>
   <si>
     <t>0.00</t>
@@ -2022,11 +2013,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2042,62 +2033,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="累计税金汇总表"/>
-      <sheetName val="累计项目税收明细表202512"/>
-      <sheetName val="累计项目税收明细表2017-202302"/>
-      <sheetName val="增值税表一 累计销项"/>
-      <sheetName val="账税差异监控"/>
-      <sheetName val="12月BS"/>
-      <sheetName val="12月PL"/>
-      <sheetName val="09月CL"/>
-      <sheetName val="收入"/>
-      <sheetName val="销项明细"/>
-      <sheetName val="进项明细"/>
-      <sheetName val="所得税明细"/>
-      <sheetName val="印花税明细"/>
-      <sheetName val="Ref 1_202512_Summary"/>
-      <sheetName val="Ref 2_202512增值税销项 （样式）"/>
-      <sheetName val="Ref 3_202512增值税进项认证清单"/>
-      <sheetName val="Ref 4_202512增值税变动表"/>
-      <sheetName val="预开票收入计提及冲回统计（导入）"/>
-      <sheetName val="未开票数监控"/>
-      <sheetName val="睿景项目累计申报"/>
-      <sheetName val="睿景项目累计缴纳"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11160,51 +11095,51 @@
       </c>
     </row>
     <row r="108" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C108" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="D108" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="E108" s="4" t="s">
+      <c r="E108" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="F108" s="4" t="s">
+      <c r="F108" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="G108" s="4" t="s">
+      <c r="G108" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="H108" s="4" t="s">
+      <c r="H108" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="I108" s="4" t="s">
+      <c r="I108" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="J108" s="4" t="s">
+      <c r="J108" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="K108" s="4" t="s">
+      <c r="K108" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="L108" s="4" t="s">
+      <c r="L108" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="M108" s="4" t="s">
+      <c r="M108" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="N108" s="4" t="s">
+      <c r="N108" s="6" t="s">
         <v>582</v>
       </c>
     </row>
     <row r="109" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="A109" s="5" t="s">
+      <c r="A109" s="4" t="s">
         <v>583</v>
       </c>
       <c r="B109" s="2" t="s">
@@ -11212,7 +11147,7 @@
       </c>
     </row>
     <row r="110" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="A110" s="5" t="s">
+      <c r="A110" s="4" t="s">
         <v>584</v>
       </c>
       <c r="B110" s="2" t="s">
@@ -11220,7 +11155,7 @@
       </c>
     </row>
     <row r="111" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="A111" s="5" t="s">
+      <c r="A111" s="4" t="s">
         <v>585</v>
       </c>
       <c r="B111" s="2" t="s">
@@ -11272,204 +11207,204 @@
       </c>
     </row>
     <row r="113" spans="1:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="A113" s="6" t="s">
+      <c r="A113" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B113" s="6" t="s">
+      <c r="B113" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="C113" s="6" t="s">
+      <c r="C113" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="D113" s="6" t="s">
+      <c r="D113" s="5">
+        <v>20160190.579999998</v>
+      </c>
+      <c r="E113" s="5">
+        <v>1209611.45</v>
+      </c>
+      <c r="F113" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="E113" s="6" t="s">
+      <c r="G113" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="H113" s="5" t="s">
         <v>603</v>
       </c>
-      <c r="F113" s="6" t="s">
+      <c r="I113" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="G113" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="H113" s="6" t="s">
+      <c r="J113" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="K113" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="L113" s="5">
+        <v>20265501.629999999</v>
+      </c>
+      <c r="M113" s="5">
+        <v>1215930.1200000001</v>
+      </c>
+      <c r="N113" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="I113" s="6" t="s">
-        <v>606</v>
-      </c>
-      <c r="J113" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="K113" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="L113" s="6">
-        <v>20265501.629999999</v>
-      </c>
-      <c r="M113" s="6">
-        <v>1215930.1200000001</v>
-      </c>
-      <c r="N113" s="6" t="s">
-        <v>607</v>
-      </c>
-      <c r="O113" s="6"/>
-      <c r="P113" s="6"/>
-      <c r="Q113" s="6"/>
-      <c r="R113" s="6"/>
-      <c r="S113" s="6"/>
-      <c r="T113" s="6"/>
-      <c r="U113" s="6"/>
+      <c r="O113" s="5"/>
+      <c r="P113" s="5"/>
+      <c r="Q113" s="5"/>
+      <c r="R113" s="5"/>
+      <c r="S113" s="5"/>
+      <c r="T113" s="5"/>
+      <c r="U113" s="5"/>
     </row>
     <row r="114" spans="1:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="A114" s="6" t="s">
+      <c r="A114" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B114" s="6" t="s">
+      <c r="B114" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="C114" s="6" t="s">
+      <c r="C114" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="E114" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="D114" s="6" t="s">
+      <c r="F114" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="H114" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="I114" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="J114" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="K114" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="L114" s="5">
+        <v>854194844.01999998</v>
+      </c>
+      <c r="M114" s="5">
+        <v>111045329.72</v>
+      </c>
+      <c r="N114" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="E114" s="6" t="s">
-        <v>610</v>
-      </c>
-      <c r="F114" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="G114" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="I114" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="J114" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="K114" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="L114" s="6">
-        <v>854194844.01999998</v>
-      </c>
-      <c r="M114" s="6">
-        <v>111045329.72</v>
-      </c>
-      <c r="N114" s="6" t="s">
-        <v>611</v>
-      </c>
-      <c r="O114" s="6"/>
-      <c r="P114" s="6"/>
-      <c r="Q114" s="6"/>
-      <c r="R114" s="6"/>
-      <c r="S114" s="6"/>
-      <c r="T114" s="6"/>
-      <c r="U114" s="6"/>
+      <c r="O114" s="5"/>
+      <c r="P114" s="5"/>
+      <c r="Q114" s="5"/>
+      <c r="R114" s="5"/>
+      <c r="S114" s="5"/>
+      <c r="T114" s="5"/>
+      <c r="U114" s="5"/>
     </row>
     <row r="115" spans="1:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="A115" s="6" t="s">
+      <c r="A115" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B115" s="6" t="s">
+      <c r="B115" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="C115" s="6" t="s">
+      <c r="C115" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="E115" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="D115" s="6" t="s">
+      <c r="F115" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="H115" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="I115" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="J115" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="K115" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="L115" s="5">
+        <v>220186683.55000001</v>
+      </c>
+      <c r="M115" s="5">
+        <v>19816801.550000001</v>
+      </c>
+      <c r="N115" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="E115" s="6" t="s">
-        <v>614</v>
-      </c>
-      <c r="F115" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="G115" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="H115" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="I115" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="J115" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="K115" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="L115" s="6">
-        <v>220186683.55000001</v>
-      </c>
-      <c r="M115" s="6">
-        <v>19816801.550000001</v>
-      </c>
-      <c r="N115" s="6" t="s">
-        <v>615</v>
-      </c>
-      <c r="O115" s="6"/>
-      <c r="P115" s="6"/>
-      <c r="Q115" s="6"/>
-      <c r="R115" s="6"/>
-      <c r="S115" s="6"/>
-      <c r="T115" s="6"/>
-      <c r="U115" s="6"/>
+      <c r="O115" s="5"/>
+      <c r="P115" s="5"/>
+      <c r="Q115" s="5"/>
+      <c r="R115" s="5"/>
+      <c r="S115" s="5"/>
+      <c r="T115" s="5"/>
+      <c r="U115" s="5"/>
     </row>
     <row r="116" spans="1:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="A116" s="6" t="s">
+      <c r="A116" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B116" s="6" t="s">
+      <c r="B116" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="C116" s="5"/>
+      <c r="D116" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="E116" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="C116" s="6"/>
-      <c r="D116" s="6" t="s">
-        <v>617</v>
-      </c>
-      <c r="E116" s="6" t="s">
-        <v>618</v>
-      </c>
-      <c r="F116" s="6" t="s">
+      <c r="F116" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="H116" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="I116" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="G116" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>605</v>
-      </c>
-      <c r="I116" s="6" t="s">
-        <v>606</v>
-      </c>
-      <c r="J116" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="K116" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="L116" s="6">
+      <c r="J116" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="K116" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="L116" s="5">
         <v>1094647029.2</v>
       </c>
-      <c r="M116" s="6">
+      <c r="M116" s="5">
         <v>132078061.39</v>
       </c>
-      <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
-      <c r="P116" s="6"/>
-      <c r="Q116" s="6"/>
-      <c r="R116" s="6"/>
-      <c r="S116" s="6"/>
-      <c r="T116" s="6"/>
-      <c r="U116" s="6"/>
+      <c r="N116" s="5"/>
+      <c r="O116" s="5"/>
+      <c r="P116" s="5"/>
+      <c r="Q116" s="5"/>
+      <c r="R116" s="5"/>
+      <c r="S116" s="5"/>
+      <c r="T116" s="5"/>
+      <c r="U116" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
